--- a/tests/workbooktests/workbooks/test_cliquetoptions.xlsx
+++ b/tests/workbooktests/workbooks/test_cliquetoptions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939C6BF0-C4E1-494B-A444-200B7A79BEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE41042-D787-4880-85AF-525353978C3D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15105" yWindow="-19605" windowWidth="21915" windowHeight="17220" xr2:uid="{18D4354C-E763-4BBF-8300-753A3273D9C3}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -39,14 +28,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -115,7 +104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,7 +153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -497,13 +486,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D84652-16FC-44DA-ACA9-77DA8AF6C3ED}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +500,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -520,34 +509,34 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03)</f>
-        <v>欣[Book1]Sheet1!R4C2YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.03,"actual365fixed")</f>
+        <v>欣[test_cliquetoptions.xlsx]Sheet1!R4C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="str" cm="1">
-        <f t="array" ref="B5">_xll.qlFlatForward(B2,0.01)</f>
-        <v>欣[Book1]Sheet1!R5C2YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="str">
+        <f>_xll.qlFlatForward(B2,0.01,"actual365fixed")</f>
+        <v>欣[test_cliquetoptions.xlsx]Sheet1!R5C2YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str" cm="1">
         <f t="array" ref="B6">_xll.qlBlackConstantVol(B2,"NullCalendar",0.25,"Act/365")</f>
-        <v>欣[Book1]Sheet1!R6C2BlackVolTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>欣[test_cliquetoptions.xlsx]Sheet1!R6C2BlackVolTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -555,16 +544,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlGeneralizedBlackScholesProcess(B7,B5,B4,B6)</f>
-        <v>欣[Book1]Sheet1!R9C2GeneralizedBlackScholesProcess,A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>欣[test_cliquetoptions.xlsx]Sheet1!R9C2GeneralizedBlackScholesProcess,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -573,7 +562,7 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R12C2PercentageStrikePayoff,A</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -582,42 +571,42 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R13C2EuropeanExercise,A</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2" t="str" cm="1">
         <f t="array" ref="B15">_xll.qlMakeSchedule(B2,B2+365,"3m")</f>
-        <v>欣[test_cliquetoptions.xlsx]Sheet1!R15C2Schedule,E</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>欣[test_cliquetoptions.xlsx]Sheet1!R15C2Schedule,A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="B16" s="1" cm="1">
         <f t="array" ref="B16:B20">_xll.qlScheduleDates(B15)</f>
         <v>46174</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="B17" s="1">
         <v>46266</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="B18" s="1">
         <v>46357</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="B19" s="1">
         <v>46447</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="B20" s="1">
         <v>46539</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="15">
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
@@ -626,12 +615,12 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R22C2CliquetOption,A</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="15">
       <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
         <v>12</v>
       </c>
@@ -640,7 +629,7 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R25C2AnalyticCliquetEngine,A</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -649,7 +638,7 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R26C2AnalyticPerformanceEngine,A</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -658,12 +647,12 @@
         <v>欣[test_cliquetoptions.xlsx]Sheet1!R27C2MCLDPerformanceEngine,A</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="15">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
         <v>12</v>
       </c>
@@ -672,7 +661,7 @@
         <v>5.3314437143560296</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -681,7 +670,7 @@
         <v>5.2783213639053736E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>14</v>
       </c>
